--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
         <v>2.55</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1959,14 +1959,14 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.15</v>
       </c>
-      <c r="N12" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2088,14 +2088,14 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N13" t="n">
         <v>2.35</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.55</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
         <v>2.56</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.89</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.78</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,23 +927,23 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2.02</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.71</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1338,37 +1338,37 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>1.71</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1596,37 +1596,37 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1710,34 +1710,34 @@
         <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y10" t="n">
         <v>2.35</v>
@@ -1746,16 +1746,16 @@
         <v>1.52</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1839,34 +1839,34 @@
         <v>4.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y11" t="n">
         <v>2.05</v>
@@ -1875,16 +1875,16 @@
         <v>1.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1968,34 +1968,34 @@
         <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y12" t="n">
         <v>2.2</v>
@@ -2004,16 +2004,16 @@
         <v>1.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2097,34 +2097,34 @@
         <v>2.35</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y13" t="n">
         <v>1.8</v>
@@ -2133,16 +2133,16 @@
         <v>1.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>4.84</v>
       </c>
       <c r="O3" t="n">
         <v>2.3</v>
@@ -813,13 +813,13 @@
         <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
         <v>2.9</v>
@@ -828,13 +828,13 @@
         <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Y3" t="n">
         <v>2.07</v>
@@ -843,16 +843,16 @@
         <v>1.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
         <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -963,41 +963,41 @@
         <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.57</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.15</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.21</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
         <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
       <c r="O5" t="n">
-        <v>2.65</v>
+        <v>4.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.08</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.8</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1209,37 +1209,37 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2.4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AB6" t="n">
         <v>1.49</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AC6" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.18</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1338,37 +1338,37 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="X7" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.48</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.14</v>
+        <v>3.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.71</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.97</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.16</v>
+        <v>2.18</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1596,37 +1596,37 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="O10" t="n">
         <v>3.55</v>
@@ -1719,10 +1719,10 @@
         <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
         <v>3.25</v>
@@ -1737,13 +1737,13 @@
         <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>4.83</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="P11" t="n">
         <v>2.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
         <v>1.42</v>
@@ -1863,28 +1863,28 @@
         <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X11" t="n">
         <v>2.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AA11" t="n">
         <v>3.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
         <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="M12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.2</v>
       </c>
-      <c r="N12" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O12" t="n">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.04</v>
+        <v>4.28</v>
       </c>
       <c r="R12" t="n">
         <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U12" t="n">
         <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4.84</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
         <v>2.3</v>
@@ -816,22 +816,22 @@
         <v>4.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
         <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
         <v>2.92</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AA4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD4" t="n">
         <v>2.45</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.33</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AA5" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.97</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>4.6</v>
+        <v>2.08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>4.8</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1209,37 +1209,37 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>2.15</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.15</v>
+        <v>2.18</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AH7" t="n">
         <v>1.27</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>1.71</v>
       </c>
       <c r="O8" t="n">
-        <v>2.08</v>
+        <v>4.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8</v>
+        <v>2.23</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="X8" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.18</v>
+        <v>1.16</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1596,37 +1596,37 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,16 +1701,16 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
@@ -1719,10 +1719,10 @@
         <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="T10" t="n">
         <v>3.25</v>
@@ -1734,10 +1734,10 @@
         <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="Y10" t="n">
         <v>2.42</v>
@@ -1771,7 +1771,7 @@
         <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
         <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="O11" t="n">
         <v>2.4</v>
@@ -1851,7 +1851,7 @@
         <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
         <v>3.04</v>
@@ -1860,10 +1860,10 @@
         <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
         <v>2.88</v>
@@ -1872,19 +1872,19 @@
         <v>2.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
         <v>3.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC11" t="n">
         <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="M12" t="n">
         <v>3.22</v>
@@ -1968,52 +1968,52 @@
         <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
         <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
         <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="O13" t="n">
         <v>3.4</v>
@@ -2124,13 +2124,13 @@
         <v>1.26</v>
       </c>
       <c r="X13" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AA13" t="n">
         <v>3.05</v>
@@ -2142,7 +2142,7 @@
         <v>1.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
         <v>1.35</v>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,53 +951,53 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.13</v>
       </c>
-      <c r="X4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1092,41 +1092,41 @@
         <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.57</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.15</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1209,37 +1209,37 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AA8" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.21</v>
+        <v>4.2</v>
       </c>
       <c r="M9" t="n">
         <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
       <c r="O9" t="n">
-        <v>2.65</v>
+        <v>4.7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1596,37 +1596,37 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X9" t="n">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.08</v>
+        <v>3.53</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
-        <v>3.8</v>
+        <v>2.49</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71</v>
+        <v>2.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.75</v>
+        <v>4.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45937.65625</v>
+        <v>45937.83333333334</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.21</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>4.25</v>
       </c>
       <c r="O5" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.23</v>
+        <v>3.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>4.25</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45937.65625</v>
+        <v>45937.89583333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="P6" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45937.65625</v>
+        <v>45937.89930555555</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
         <v>1.26</v>
       </c>
       <c r="X7" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AA7" t="n">
         <v>3.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,780 +1393,6 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45937.65625</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>45937</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Wales Welsh Premier League</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Caernarfon Town</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>The New Saints</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>45937.65625</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45937</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Wales Welsh Premier League</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Llanelli Town</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Cardiff MU</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3" t="n">
-        <v>45937.65625</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45937</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>45937.83333333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45937</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="3" t="n">
-        <v>45937.89583333334</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>45937</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Paysandu</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="3" t="n">
-        <v>45937.89930555555</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45937</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Hartford Athletic</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
         <v>45937.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-07.xlsx
+++ b/jogos_2025-10-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK7"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.53</v>
+        <v>2.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="X4" t="n">
-        <v>2.49</v>
+        <v>3.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.42</v>
+        <v>1.71</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.83</v>
+        <v>2.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>2.18</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45937.83333333334</v>
+        <v>45937.65625</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X5" t="n">
         <v>4.25</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Y5" t="n">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45937.89583333334</v>
+        <v>45937.65625</v>
       </c>
     </row>
     <row r="6">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45937.89930555555</v>
+        <v>45937.65625</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,85 +1314,859 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>1.26</v>
       </c>
       <c r="X7" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
         <v>3.05</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="n">
+        <v>45937.65625</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wales Welsh Premier League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Caernarfon Town</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The New Saints</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>45937.65625</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wales Welsh Premier League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Llanelli Town</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cardiff MU</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="n">
+        <v>45937.65625</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="V10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>45937.83333333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>45937.89583333334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>45937.89930555555</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AD13" t="n">
         <v>2</v>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>1.26</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AH13" t="n">
         <v>1.35</v>
       </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="3" t="n">
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>45937.95833333334</v>
       </c>
     </row>
